--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_rf_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_rf_monthly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>4.829376344876708</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -958,27 +959,27 @@
         <v>1.295281120905988</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -986,11 +987,11 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
@@ -998,7 +999,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1006,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1095,27 +1096,27 @@
         <v>2.985170616228376</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1123,19 +1124,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1143,7 +1144,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1236,27 +1237,27 @@
         <v>3.403855809213878</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1266,19 +1267,19 @@
         <v>0.07191433725276419</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1286,15 +1287,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
@@ -1302,15 +1303,15 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -1393,19 +1394,19 @@
         <v>5.671621587955389</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
@@ -1413,7 +1414,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1421,19 +1422,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1534,27 +1535,27 @@
         <v>5.064071665862063</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1564,35 +1565,35 @@
         <v>0.1808699199865536</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
@@ -1600,15 +1601,15 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1691,11 +1692,11 @@
         <v>5.264458902144272</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
@@ -1703,7 +1704,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1719,11 +1720,11 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
@@ -1731,7 +1732,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1739,7 +1740,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1832,27 +1833,27 @@
         <v>4.772384040864172</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="n">
@@ -1862,11 +1863,11 @@
         <v>0.1741447151948083</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF10" s="2" t="n">
@@ -1874,7 +1875,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
@@ -1882,15 +1883,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
@@ -1898,15 +1899,15 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -2151,28 +2152,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196767172</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208222</v>
+        <v>0.08831268540851216</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997946</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798223</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2181,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278816</v>
+        <v>0.2724034021441992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2193,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668942</v>
+        <v>-0.08310591627222952</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2239,49 +2240,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.2064468322738722</v>
+        <v>0.03447263601447603</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.3307838900705071</v>
+        <v>-0.02079384374649318</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1429549412877313</v>
+        <v>0.1100517970205884</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2002183608269251</v>
+        <v>0.318256905013339</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9706371191135734</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3754608976947176</v>
+        <v>-0.1959391460331659</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.1793967126992393</v>
+        <v>-0.03156858624818237</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7980738484849268</v>
+        <v>1.154425856129244</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.9317394664652177</v>
+        <v>0.2865601290137498</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1283598434192632</v>
+        <v>0.011125973764055</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.308643346593946</v>
+        <v>1.051969713880653</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1397690308849029</v>
+        <v>-0.08580900226837973</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2333,58 +2334,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.3050913934539505</v>
+        <v>0.07488442474097812</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4395948126489193</v>
+        <v>0.01745895379357942</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1109469294357623</v>
+        <v>0.07812037677756986</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1530752451527519</v>
+        <v>0.2757884445827267</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9518005540166204</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2627477773058103</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.3922472502781837</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5584925916461387</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.770210184900723</v>
+        <v>0.2733293632849492</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.03400801284489896</v>
+        <v>0.0007277260805729213</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.081772824084672</v>
+        <v>1.003399227518678</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655971</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.08176453246112492</v>
+        <v>0.03906511136166646</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1804740807626992</v>
+        <v>0.04986171078189039</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.08361856470224116</v>
+        <v>-0.01028383006004008</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2435,58 +2436,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.2468323023570769</v>
+        <v>-0.1428941070710085</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.3753315083674176</v>
+        <v>-0.1886848064432678</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1219414188912732</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.03371580389160611</v>
+        <v>0.1287326796619276</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09770524133585029</v>
+        <v>0.2295526434170264</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7096952908587257</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.04000360934778335</v>
+        <v>-0.1959391460331659</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.9639712446068007</v>
+        <v>-0.03156858624818237</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.08503105026780057</v>
+        <v>1.154425856129244</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1219414188912732</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1988730530839231</v>
+        <v>0.06597142330765093</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2997191215787033</v>
+        <v>-0.1622378394215844</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2793204614616548</v>
+        <v>0.2421828170586811</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1002150837798468</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.03347472014749919</v>
+        <v>-0.1714561960467387</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.6652337788121661</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.3793816019726127</v>
+        <v>-0.1714561960467387</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2541,67 +2542,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1736145666245639</v>
+        <v>0.03276450336018755</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2945679135087682</v>
+        <v>-0.02241071977834352</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3642340500887142</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1392203501052228</v>
+        <v>0.1049327105339339</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1637986200429615</v>
+        <v>0.2984874380730844</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9734072022160665</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3048758663043974</v>
+        <v>-0.1959391460331659</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.3126914154331981</v>
+        <v>-0.03156858624818237</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6480394028396574</v>
+        <v>1.154425856129244</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3642340500887142</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.688352496675787</v>
+        <v>0.2844357467038021</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01380636889321674</v>
+        <v>0.00945639137660792</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9668023597879095</v>
+        <v>1.04417105096666</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.0542294413365596</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.02721401786718369</v>
+        <v>-0.001651211056552859</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1130193948301692</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1259936829032079</v>
+        <v>-0.00165121105655297</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1007414710485759</v>
+        <v>-0.03918553512480238</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.05714203050434441</v>
+        <v>-0.04749359869954251</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.04624179033831888</v>
+        <v>0.00872231783786126</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -2649,58 +2650,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1437042766908729</v>
+        <v>-0.07381122855509259</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.05545398004130697</v>
+        <v>-0.1232926659656618</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.537556826654351</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.3290364637781537</v>
+        <v>0.1256636113461165</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1789140368119662</v>
+        <v>0.2417963151658988</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.997229916897507</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4565044795311197</v>
+        <v>-0.1959391460331659</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.0263517974162526</v>
+        <v>-0.03156858624818237</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9703388264048647</v>
+        <v>1.154425856129244</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.5081633255643593</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.575534095608351</v>
+        <v>0.1518888985523361</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.07970539698327406</v>
+        <v>-0.09471406897276236</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.8083470670327658</v>
+        <v>0.5575881114433818</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1397690308849028</v>
+        <v>-0.02035030842906338</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2902333526830947</v>
+        <v>-0.1046754266857701</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.1297654246743818</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1843961761099528</v>
+        <v>-0.1046754266857701</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2755,67 +2756,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.0265794055326718</v>
+        <v>0.03525039506820882</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1323792298299231</v>
+        <v>-0.02005763630418589</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4519459771853966</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.229492260485587</v>
+        <v>0.1051418109895207</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1894376607746025</v>
+        <v>0.3008772397074883</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9977839335180055</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.427556347586593</v>
+        <v>-0.1959391460331659</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08101824108348987</v>
+        <v>-0.03156858624818237</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.90880712707408</v>
+        <v>1.154425856129244</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4519459771853966</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.7933283061217307</v>
+        <v>0.2875274178077456</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.04751167630155351</v>
+        <v>0.01188617983735352</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.114242604114918</v>
+        <v>1.0555206562932</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1397690308849028</v>
+        <v>-0.0542294413365596</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.1490885648082743</v>
+        <v>0.0007518411088467403</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-0.08341423251095414</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.07165104960906443</v>
+        <v>0.0007518411088467403</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.2134042024322842</v>
+        <v>-0.03687282907864275</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.2235443518617167</v>
+        <v>-0.04749359869954251</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.01305953463503773</v>
+        <v>0.01115033936401821</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -2863,67 +2864,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.4010796063471338</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.5454756222608497</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1674959463385509</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.07393834888720115</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1060517778278873</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.8869806094182825</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.06009552032813315</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.7749413118963213</v>
+        <v>0.2117597153840092</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.127738103966218</v>
+        <v>-0.03587709265072067</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1674959463385509</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4906616966399282</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1292807193666101</v>
+        <v>-0.2060850325577077</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6891423921027062</v>
+        <v>0.03737143334716839</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1249679055822545</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.161327270184318</v>
+        <v>-0.01753663532123917</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.5049569773974376</v>
+        <v>0.2512602319347623</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2283319140507043</v>
+        <v>-0.2148209144634718</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>0.04878377108627574</v>
+        <v>0.09933463918678509</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.03905676935899827</v>
+        <v>-0.08094202744966106</v>
       </c>
     </row>
     <row r="10">
@@ -2973,73 +2974,73 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.165685123116978</v>
+        <v>0.07488442474097812</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.2858212572991194</v>
+        <v>0.01745895379357942</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3907546470334907</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.145192829142484</v>
+        <v>0.07812037677756986</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1651075038384782</v>
+        <v>0.2757884445827267</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9761772853185595</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3353927898423992</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.2550624228375991</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7129057011983638</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3907546470334907</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.7539459477735049</v>
+        <v>0.2733293632849492</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.02450781244169287</v>
+        <v>0.0007277260805729213</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.058929436560575</v>
+        <v>1.003399227518678</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655971</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.03378657729994428</v>
+        <v>0.03906511136166646</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.06415628373695115</v>
+        <v>0.04986171078189039</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.09203804228167856</v>
+        <v>-0.01028383006004008</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.106817247463437</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.09853481658029783</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.009187743504102786</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>0.04878377108627574</v>
+        <v>0.09933463918678509</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>-0.04773491163227539</v>
+        <v>-0.01680582695486188</v>
       </c>
     </row>
   </sheetData>
@@ -3283,28 +3284,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05390587101818811</v>
+        <v>-0.09123360655355661</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2215345333965962</v>
+        <v>0.2716992530341495</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389368129070568</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4707583434268612</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3313,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.122709994261599</v>
+        <v>0.7171104771509156</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3325,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756423</v>
+        <v>-0.1395291740668942</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3371,49 +3372,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.05847752440067311</v>
+        <v>0.2071638246975345</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.1066351355555943</v>
+        <v>0.3283543861249494</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.3957852429007653</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2927826980910351</v>
+        <v>0.1430341619260324</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2857263117276639</v>
+        <v>0.2003292571814022</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.971159179145868</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.6055610031715249</v>
+        <v>-0.3754722955855372</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.205546127297479</v>
+        <v>0.1800426074891857</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.202680982991053</v>
+        <v>0.7975903153458862</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.3957852429007653</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.386991355240556</v>
+        <v>0.9329227769476338</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1245018686930377</v>
+        <v>0.1256834098146096</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.23539592800434</v>
+        <v>1.300947073948971</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1935283927621277</v>
+        <v>-0.1397690308849029</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3465,58 +3466,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.2553938843122963</v>
+        <v>0.3109354176354568</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1911821718000761</v>
+        <v>0.442543900268815</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1742196764528615</v>
+        <v>0.1110081735734261</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2118070551778035</v>
+        <v>0.1531549489989729</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9517470881863561</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.2609524087912378</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>0.3964274769943947</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>0.5543234919463098</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.306850557115716</v>
+        <v>0.7738173200609908</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.08674786633685749</v>
+        <v>0.03302457451902874</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.164014361496109</v>
+        <v>1.079076857355887</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.3333658163743507</v>
+        <v>0.08596314006006867</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3796874128847996</v>
+        <v>0.1833703869096881</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03357397920561933</v>
+        <v>-0.08231340578328417</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3567,68 +3568,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.08539902236343266</v>
+        <v>0.2465760498584322</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.02988231891603244</v>
+        <v>0.3717233150874621</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1788222766520315</v>
+        <v>-0.1219414188912731</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.05124267446933404</v>
+        <v>0.03372620420688702</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.08859164174962927</v>
+        <v>0.09775943598338378</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3488372093023256</v>
+        <v>0.7099278979478647</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>0.03998462919498347</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499055</v>
+        <v>0.9650468104285783</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389797</v>
+        <v>-0.0849366341633319</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1219414188912731</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.0618161627323448</v>
+        <v>0.1986485327416463</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.4997827467705001</v>
+        <v>-0.3019386063437909</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.05505977772381102</v>
+        <v>0.2770124535495258</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1788222766520315</v>
+        <v>-0.1002150837798468</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.152812652371916</v>
+        <v>0.03264861351422033</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>1.591553916774709</v>
+        <v>0.6652337788121663</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5551654762380414</v>
+        <v>-0.3798776924577987</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1158795430432833</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.08262100919868676</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3677,74 +3674,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1425479737191842</v>
+        <v>0.1759845641446183</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.08410817810072357</v>
+        <v>0.2940449521738646</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3642340500887141</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1775332588634217</v>
+        <v>0.1392974936426376</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2179776410316156</v>
+        <v>0.1638875645011864</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9738372093023255</v>
+        <v>0.9739323349972269</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.3048885523779399</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>0.3134103088614282</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>0.6476540599546666</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3642340500887141</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.09949041702506</v>
+        <v>0.6917928314482518</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.01093864790730226</v>
+        <v>-0.01474433127021135</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9793182768878703</v>
+        <v>0.9646949159029847</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1788222766520314</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.2135110985979323</v>
+        <v>-0.02582852460868634</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3796874128847996</v>
+        <v>0.113019394830169</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1204449013123979</v>
+        <v>-0.1247488768693394</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.08988884843495071</v>
+        <v>-0.1029424117125849</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.05944968106159654</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.0898888484349506</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1158795430432833</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>0.00492481533305944</v>
-      </c>
+        <v>-0.04624179033831888</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3789,58 +3782,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.09781903008507875</v>
+        <v>-0.1431953793821785</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.04166705990969177</v>
+        <v>-0.05717836091138884</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3389624169517775</v>
+        <v>-0.5375568266543511</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1571129228338186</v>
+        <v>0.3291916255077421</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1437815448883416</v>
+        <v>0.1790131831237831</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9774709302325582</v>
+        <v>0.9977814753189129</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3079426187795978</v>
+        <v>-0.4565143983697967</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3938978424133903</v>
+        <v>0.02691387739448681</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.6115927702064764</v>
+        <v>0.9697425542086489</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3366856651000728</v>
+        <v>-0.5081633255643594</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5863121467603449</v>
+        <v>0.5764992081626585</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2526948329971209</v>
+        <v>-0.08188830646561762</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.5222293822599838</v>
+        <v>0.803919656080181</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1788222766520318</v>
+        <v>-0.1397690308849028</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1660040610143281</v>
+        <v>-0.2902333526830947</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.7545359023447391</v>
+        <v>-0.1297654246743817</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3354344818729015</v>
+        <v>-0.184396176109953</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3895,67 +3888,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.06442704985655712</v>
+        <v>0.02718950258491182</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.009983034659636569</v>
+        <v>0.1303119371408044</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5042271545140171</v>
+        <v>-0.4519459771853965</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2228887754365696</v>
+        <v>0.2296193819681661</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2287177615410679</v>
+        <v>0.1895426128920633</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9883720930232558</v>
+        <v>0.9983361064891847</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.5042271545140169</v>
+        <v>-0.4275667947310976</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.001445951733913375</v>
+        <v>0.0816102590552501</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.001425796353551</v>
+        <v>0.9082511243850657</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.5042271545140171</v>
+        <v>-0.4519459771853965</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.147005548101669</v>
+        <v>0.7944268311660683</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.0114455360862995</v>
+        <v>0.04502701197388204</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.021640097589092</v>
+        <v>1.10781651708999</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1788222766520317</v>
+        <v>-0.1397690308849028</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1305381203767815</v>
+        <v>-0.1490885648082743</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.2569062630021186</v>
+        <v>-0.08341423251095414</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1005390348867441</v>
+        <v>-0.07165104960906443</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1521170660795043</v>
+        <v>-0.2164453803241806</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.08899200553403375</v>
+        <v>-0.2254447317355446</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.06929144522214015</v>
+        <v>0.01161873371738698</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -4003,64 +3996,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.01140744678583938</v>
+        <v>0.4016192418823157</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.04032468686343937</v>
+        <v>0.5423317279226807</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2588265729313863</v>
+        <v>-0.1674959463385508</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1537794068446022</v>
+        <v>0.07397932191069892</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1286574678610456</v>
+        <v>0.1061101915776842</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9949127906976745</v>
+        <v>0.8874098724348308</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2130444132454079</v>
+        <v>-0.06030912865523896</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.5850357560207051</v>
+        <v>0.7755421548433989</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4231191622327169</v>
+        <v>0.1281105890045873</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2230337991988246</v>
+        <v>-0.1674959463385508</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.2852154096229085</v>
+        <v>0.4915748195749781</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3945402748857456</v>
+        <v>-0.1313460377634836</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2540419263039457</v>
+        <v>0.6854938468170314</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1788222766520315</v>
+        <v>-0.1249679055822545</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.07422549434311398</v>
+        <v>0.1610845298760537</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.9951262250492083</v>
+        <v>0.5046424117017918</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.4615751721089131</v>
+        <v>-0.2283319140507043</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.04880291182708141</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.03885587127619017</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4109,70 +4106,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.09241635861607511</v>
+        <v>0.1692396118105475</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.03654072783623619</v>
+        <v>0.2866228551611318</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.5010679419770513</v>
+        <v>-0.3907546470334906</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.2229855947157678</v>
+        <v>0.14527311496322</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2245879178366804</v>
+        <v>0.1651962128696235</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9803779069767442</v>
+        <v>0.9761508596783139</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.5010679419770512</v>
+        <v>-0.3337743276351042</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.00491713268437044</v>
+        <v>0.258830751681064</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.9951514081093668</v>
+        <v>0.7090141519434602</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.5010679419770513</v>
+        <v>-0.3907546470334906</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>1.189509254917086</v>
+        <v>0.7550203486757079</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.03146885859871018</v>
+        <v>0.0220777125463083</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.059498232844556</v>
+        <v>1.052864757569027</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1788222766520315</v>
+        <v>-0.1175306843923517</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.1602658321254589</v>
+        <v>-0.03141596203521857</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.2649156448390255</v>
+        <v>0.06676720288898585</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.08273264161175298</v>
+        <v>-0.09203804228167856</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.1298218254309086</v>
+        <v>-0.10808755635002</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.0831867906990591</v>
+        <v>-0.09853481658029783</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.05086645159422165</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>-0.01059690373563194</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.04880291182708141</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.05006558616960655</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4415,28 +4416,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093203</v>
+        <v>0.05390587101818811</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.0812675747870259</v>
+        <v>0.2215345333965962</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962869</v>
+        <v>0.2389368129070568</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4445,10 +4446,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165606</v>
+        <v>1.122709994261599</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4457,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756423</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4503,49 +4504,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.05464279041512032</v>
+        <v>-0.05847752440067311</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.03051848596557694</v>
+        <v>-0.1066351355555943</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.05565303537278199</v>
+        <v>0.2927826980910351</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1949988330089462</v>
+        <v>0.2857263117276639</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>1</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.6055610031715249</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.02460204642762664</v>
+        <v>-0.205546127297479</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8987197269483773</v>
+        <v>1.202680982991053</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.279351969925393</v>
+        <v>1.386991355240556</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.005774378021768278</v>
+        <v>0.1245018686930377</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.027003168811594</v>
+        <v>1.23539592800434</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02998688672969829</v>
+        <v>-0.1935283927621277</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4597,58 +4598,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.2553938843122963</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>0.1911821718000761</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.1742196764528615</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.2118070551778035</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>1.306850557115716</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>0.08674786633685749</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>1.164014361496109</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1243810385007439</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03383043031830058</v>
+        <v>0.3333658163743507</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.04011147910134616</v>
+        <v>0.3796874128847996</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.07109036954724546</v>
+        <v>-0.03357397920561933</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4699,64 +4700,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.05464279041512032</v>
+        <v>0.08539902236343266</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03051848596557694</v>
+        <v>0.02988231891603244</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.1788222766520315</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.05565303537278199</v>
+        <v>0.05124267446933404</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1949988330089462</v>
+        <v>0.08859164174962927</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1756429698727684</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.02460204642762664</v>
+        <v>1.058870045499055</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8987197269483773</v>
+        <v>-0.04411026616389797</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.279351969925393</v>
+        <v>0.0618161627323448</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.005774378021768278</v>
+        <v>-0.4997827467705001</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.027003168811594</v>
+        <v>0.05505977772381102</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02998688672969829</v>
+        <v>-0.1788222766520315</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0</v>
+        <v>0.152812652371916</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>1.591553916774709</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.5551654762380414</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1158795430432833</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.08262100919868676</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4805,70 +4810,74 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.05464279041512032</v>
+        <v>0.1425479737191842</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.03051848596557694</v>
+        <v>0.08410817810072357</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.05565303537278199</v>
+        <v>0.1775332588634217</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1949988330089462</v>
+        <v>0.2179776410316156</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9738372093023255</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.02460204642762664</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8987197269483773</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.279351969925393</v>
+        <v>1.09949041702506</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.005774378021768278</v>
+        <v>-0.01093864790730226</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.027003168811594</v>
+        <v>0.9793182768878703</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02998688672969829</v>
+        <v>-0.1788222766520314</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>0.2135110985979323</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.3796874128847996</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1204449013123979</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.03501500293519477</v>
+        <v>-0.08988884843495071</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.03856459611041152</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.07653098559500959</v>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+        <v>-0.0898888484349506</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1158795430432833</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.00492481533305944</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4913,58 +4922,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.03431494793841328</v>
+        <v>0.09781903008507875</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01065563036894668</v>
+        <v>0.04166705990969177</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.07224947285461214</v>
+        <v>-0.3389624169517775</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03187297595698499</v>
+        <v>0.1571129228338186</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1023221197623363</v>
+        <v>0.1437815448883416</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.9774709302325582</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.03488472212103899</v>
+        <v>-0.3079426187795978</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1995519569969946</v>
+        <v>0.3938978424133903</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.1784961160813924</v>
+        <v>0.6115927702064764</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.07224947285461214</v>
+        <v>-0.3366856651000728</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.07170093733417304</v>
+        <v>0.5863121467603449</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1574724008628506</v>
+        <v>-0.2526948329971209</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2635996798899382</v>
+        <v>0.5222293822599838</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.01963022439886797</v>
+        <v>-0.1788222766520318</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.01927462327666962</v>
+        <v>0.1660040610143281</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.170749132484507</v>
+        <v>0.7545359023447391</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1623095422312355</v>
+        <v>-0.3354344818729015</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5019,67 +5028,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.03089948295642841</v>
+        <v>0.06442704985655712</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.007318292045400909</v>
+        <v>0.009983034659636569</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1532653413160446</v>
+        <v>-0.5042271545140171</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.05194847930026126</v>
+        <v>0.2228887754365696</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1727582908343249</v>
+        <v>0.2287177615410679</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9883720930232558</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1530640146787772</v>
+        <v>-0.5042271545140169</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.05266566795626293</v>
+        <v>-0.001445951733913375</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7831890429624336</v>
+        <v>1.001425796353551</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1532653413160446</v>
+        <v>-0.5042271545140171</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.217210628457867</v>
+        <v>1.147005548101669</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.04307861203348928</v>
+        <v>0.0114455360862995</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7985481676945557</v>
+        <v>1.021640097589092</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1788222766520317</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.02251312735883426</v>
+        <v>0.1305381203767815</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.02738977696412248</v>
+        <v>0.2569062630021186</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.04857251399796558</v>
+        <v>-0.1005390348867441</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.01171357835581066</v>
+        <v>-0.1521170660795043</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.01223109483246476</v>
+        <v>-0.08899200553403375</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.02424116922795228</v>
+        <v>-0.06929144522214015</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -5127,58 +5136,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.06662225039212788</v>
+        <v>0.01140744678583938</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.04222392317179158</v>
+        <v>-0.04032468686343937</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.07224947285461214</v>
+        <v>-0.2588265729313863</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.02987211560149754</v>
+        <v>0.1537794068446022</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1086724749001501</v>
+        <v>0.1286574678610456</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>0.9949127906976745</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.03488472212103899</v>
+        <v>-0.2130444132454079</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1995519569969946</v>
+        <v>0.5850357560207051</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1784961160813924</v>
+        <v>0.4231191622327169</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.07224947285461214</v>
+        <v>-0.2230337991988246</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1051760083378324</v>
+        <v>0.2852154096229085</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1311556643357608</v>
+        <v>-0.3945402748857456</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3866666623999699</v>
+        <v>0.2540419263039457</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.02093970974885051</v>
+        <v>-0.1788222766520315</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.01135878430676263</v>
+        <v>0.07422549434311398</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.170749132484507</v>
+        <v>0.9951262250492083</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1361438960364582</v>
+        <v>-0.4615751721089131</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5233,67 +5242,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.04747890464749061</v>
+        <v>0.09241635861607511</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.02351846967382176</v>
+        <v>0.03654072783623619</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1532653413160446</v>
+        <v>-0.5010679419770513</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.05077853630876075</v>
+        <v>0.2229855947157678</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.173950039431866</v>
+        <v>0.2245879178366804</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9803779069767442</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1530640146787772</v>
+        <v>-0.5010679419770512</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.05266566795626293</v>
+        <v>0.00491713268437044</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7831890429624336</v>
+        <v>0.9951514081093668</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1532653413160446</v>
+        <v>-0.5010679419770513</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.2367863956686247</v>
+        <v>1.189509254917086</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.02768894167416913</v>
+        <v>0.03146885859871018</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.8705160688435456</v>
+        <v>1.059498232844556</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1788222766520315</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.00679271297612527</v>
+        <v>0.1602658321254589</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.02738977696412248</v>
+        <v>0.2649156448390255</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03327119921443555</v>
+        <v>-0.08273264161175298</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.02798444309427262</v>
+        <v>-0.1298218254309086</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.01223109483246476</v>
+        <v>-0.0831867906990591</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.04071350871276547</v>
+        <v>-0.05086645159422165</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5539,28 +5548,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714601</v>
+        <v>0.01891210187562598</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.08099293800752018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886583</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348786</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5569,10 +5578,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473792</v>
+        <v>0.2720069211165606</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5581,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886086</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5627,49 +5636,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.03121918450036776</v>
+        <v>0.05118637363330114</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.1175464974290086</v>
+        <v>0.031675226644442</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1525896620499075</v>
+        <v>0.05752531060341064</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.507010924502074</v>
+        <v>0.194384405087508</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793301</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.07186081874535022</v>
+        <v>0.02575214599681663</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.175747595702974</v>
+        <v>0.8963267075789259</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4705792374445794</v>
+        <v>0.279351969925393</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.04922287476529197</v>
+        <v>0.005774378021768278</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8607428943883418</v>
+        <v>1.027003168811594</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.09590060655538413</v>
+        <v>-0.02998688672969829</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5721,58 +5730,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.0009544101684616502</v>
+        <v>0.01970412365980478</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08997859384708495</v>
+        <v>0.0007773210100467942</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1202708276706985</v>
+        <v>0.04505087866076889</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.428252010780779</v>
+        <v>0.1645456863596117</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.07118238373413943</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7134331218450367</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4189993189650008</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08257096330288938</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7663973627717755</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.03124006364256671</v>
+        <v>-0.02994925615776556</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.06872512632346761</v>
+        <v>0.04428968334565297</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.03507455917112556</v>
+        <v>-0.07109036954724546</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5823,58 +5832,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.27700745648557</v>
+        <v>0.05118637363330114</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.3414327656478444</v>
+        <v>0.031675226644442</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.262142851685752</v>
+        <v>0.05752531060341064</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4331244149524727</v>
+        <v>0.194384405087508</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793301</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07186081874535022</v>
+        <v>0.02575214599681663</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.175747595702974</v>
+        <v>0.8963267075789259</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.09748026210782346</v>
+        <v>0.279351969925393</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2904434510975922</v>
+        <v>0.005774378021768278</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1783024754939465</v>
+        <v>1.027003168811594</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.06909011814875743</v>
+        <v>-0.02998688672969829</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2537088555561881</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2537088555561881</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5929,67 +5938,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.06547799841225554</v>
+        <v>0.05118637363330114</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1487525347976177</v>
+        <v>0.031675226644442</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1683347931404922</v>
+        <v>0.05752531060341064</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4794728561959459</v>
+        <v>0.194384405087508</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793301</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.07186081874535022</v>
+        <v>0.02575214599681663</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.175747595702974</v>
+        <v>0.8963267075789259</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4185754202423189</v>
+        <v>0.279351969925393</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08284502756184253</v>
+        <v>0.005774378021768278</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7656220038429156</v>
+        <v>1.027003168811594</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07538615706116913</v>
+        <v>-0.02998688672969829</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.03536281206623537</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.03536281206623548</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.06458522904312503</v>
+        <v>0.03087390669805656</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.0643057083909776</v>
+        <v>-0.04241130028572093</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.000298730744276221</v>
+        <v>0.07653098559500959</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -6037,68 +6046,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0391494778206698</v>
+        <v>0.03092515228795079</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.05344833245408653</v>
+        <v>0.01179007530699749</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.09590060655538424</v>
+        <v>-0.07507015460038857</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.04019284238938762</v>
+        <v>0.03432914938917885</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1465690030598211</v>
+        <v>0.1020732133824969</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.4180327868852459</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.0007182735616988456</v>
+        <v>-0.03804772733301032</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4098984628208118</v>
+        <v>0.2008984350698941</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.002474931135736743</v>
+        <v>0.1912207157992956</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.07507015460038857</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.03840361995408448</v>
+        <v>0.07170093733417304</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.3286384143918215</v>
+        <v>-0.1574724008628506</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.07024458446949979</v>
+        <v>0.2635996798899382</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.09590060655538446</v>
+        <v>-0.01963022439886797</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.07263630864195636</v>
+        <v>-0.01927462327666962</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.5190593084486794</v>
+        <v>0.170749132484507</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2938812180168442</v>
+        <v>-0.1623095422312355</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.03001018564506341</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.02853447743218596</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6147,74 +6152,70 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.006563719865421369</v>
+        <v>0.02752088092582339</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.08313039859482585</v>
+        <v>0.008448990874041273</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1198665936154176</v>
+        <v>0.05404514951330967</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4381216431209135</v>
+        <v>0.1722226783087019</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.05384726849613908</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7832210327804745</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4296777319489062</v>
+        <v>0.217210628457867</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.07566702331761588</v>
+        <v>-0.04307861203348928</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7859293934434928</v>
+        <v>0.7985481676945557</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.09590060655538435</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.03900046714519556</v>
+        <v>-0.02251312735883437</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.06872512632346761</v>
+        <v>0.02738977696412226</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02781319391313286</v>
+        <v>-0.04857251399796558</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.007525312268432893</v>
+        <v>0.007665711145664167</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0</v>
+        <v>-0.01618315937718295</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.007525312268433115</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.03001018564506341</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.009449106185097977</v>
-      </c>
+        <v>0.02424116922795228</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6259,58 +6260,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.0534042120417586</v>
+        <v>0.06312657291760981</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1377546342390233</v>
+        <v>0.04339380301852658</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1393867712832274</v>
+        <v>-0.07507015460038857</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0957694643440474</v>
+        <v>0.03207900575911054</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1283334894321922</v>
+        <v>0.1084077612637362</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.8835616438356164</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.09810363394876553</v>
+        <v>-0.03804772733301032</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2706696117315508</v>
+        <v>0.2008984350698941</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.3380324031619028</v>
+        <v>0.1912207157992956</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1393867712832274</v>
+        <v>-0.07507015460038857</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.04956159442432839</v>
+        <v>0.1051760083378324</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3214244223673621</v>
+        <v>-0.1311556643357608</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.09065378758943145</v>
+        <v>0.3866666623999699</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0009963797895713444</v>
+        <v>-0.02093970974885051</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.02289994515420835</v>
+        <v>0.01135878430676263</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3690507171713961</v>
+        <v>0.170749132484507</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.286293748952863</v>
+        <v>-0.1361438960364582</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6365,67 +6366,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.01746335766058227</v>
+        <v>0.04404596631279611</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.1050164417329031</v>
+        <v>0.02466735294526723</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3140368405715118</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1396236973530398</v>
+        <v>0.05274719927873149</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4307602182183422</v>
+        <v>0.1734137768760435</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3140368405715118</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.03355576731126375</v>
+        <v>0.05384726849613908</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.082066215357512</v>
+        <v>0.7832210327804745</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3140368405715118</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.43234607986531</v>
+        <v>0.2367863956686247</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.07394184993254005</v>
+        <v>-0.02768894167416913</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7908101049709982</v>
+        <v>0.8705160688435456</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.01419911152213627</v>
+        <v>-0.00679271297612527</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.04127080529269977</v>
+        <v>0.02738977696412226</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.02599870622796696</v>
+        <v>-0.03327119921443555</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.01652471885182372</v>
+        <v>0.02387147613527962</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.02568885146849087</v>
+        <v>-0.01618315937718295</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.009405755677208028</v>
+        <v>0.04071350871276547</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -6671,28 +6672,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363066</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752891</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.4518304992174232</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450097</v>
+        <v>-0.2902196151348786</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6701,10 +6702,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682992</v>
+        <v>0.5657770181230022</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6713,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.05185156587886086</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6759,49 +6760,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1385354644109973</v>
+        <v>-0.03998309990267035</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.07306049421285321</v>
+        <v>-0.1361765872876155</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1790388907472599</v>
+        <v>0.1503162255013063</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2472263231475021</v>
+        <v>0.4989097639400619</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9512670565302144</v>
+        <v>1</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3372034926825385</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.03966012176582068</v>
+        <v>-0.07186081874535022</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.088345406940788</v>
+        <v>1.175747595702974</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3372034926825385</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7177752927802767</v>
+        <v>0.4572758856201522</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1173757526199353</v>
+        <v>-0.06929539215802083</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.335818324857759</v>
+        <v>0.8082263347090188</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1166039321461161</v>
+        <v>-0.09590060655538413</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6853,58 +6854,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.05550959933794908</v>
+        <v>0.001402698831345583</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.005190714109256422</v>
+        <v>-0.09893763670599443</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1161134555088488</v>
+        <v>0.1183626651723915</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1734081721485486</v>
+        <v>0.4213989939818436</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9727095516569201</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2377598766809244</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1044258367867865</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7673849036436503</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3847468363930642</v>
+        <v>0.4223472503301919</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09925207039248651</v>
+        <v>-0.09160293332491798</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7160345022383415</v>
+        <v>0.7464906434894674</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07769789874505417</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.07292338944926957</v>
+        <v>0.04310944810431994</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.150036421290288</v>
+        <v>0.06872512632346761</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1938719562371833</v>
+        <v>-0.02396844388534991</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -6955,68 +6956,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.002069232786839126</v>
+        <v>-0.2769955331494085</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.05945829907902977</v>
+        <v>-0.34944042558224</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2944964900151588</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1756474029500087</v>
+        <v>0.2626236095180795</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2081723177968694</v>
+        <v>0.4262030319420221</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9590643274853801</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2852743938399765</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.03558104789742011</v>
+        <v>-0.07186081874535022</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.9207409857579846</v>
+        <v>1.175747595702974</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2935130093570599</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3962431996451086</v>
+        <v>0.09749836136239121</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.09177393422698499</v>
+        <v>-0.2990711010192031</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7374298509718111</v>
+        <v>0.172326478876515</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.09816470117601528</v>
+        <v>-0.06909011814875743</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1234961067028122</v>
+        <v>-0.2468836050935239</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.07834847991691252</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1871793676894478</v>
+        <v>-0.2468836050935239</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.7987676932469374</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.4433148926414667</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7065,74 +7062,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.04258757152117965</v>
+        <v>-0.06327312383708039</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.01736962112509388</v>
+        <v>-0.1571329558214772</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3176543999139079</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1782173967914346</v>
+        <v>0.1660823274172656</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2265591129258874</v>
+        <v>0.4717956818415567</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9844054580896686</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3167032016699218</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.009956816516820788</v>
+        <v>-0.07186081874535022</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.022179432837026</v>
+        <v>1.175747595702974</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3167032016699219</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5258194887919554</v>
+        <v>0.4219223514774815</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.007487354826476555</v>
+        <v>-0.09187429945674419</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9785782761829468</v>
+        <v>0.7457396429378365</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0981647011760155</v>
+        <v>-0.07538615706116913</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.08427308229652264</v>
+        <v>-0.02426001451854531</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03092999251849937</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1117467487133514</v>
+        <v>-0.0242600145185452</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.01224245409504054</v>
+        <v>-0.06458522904312503</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.1035675275728717</v>
+        <v>-0.0643057083909776</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.1018761326556643</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.7987676932469374</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.07008181681004189</v>
-      </c>
+        <v>-0.0002987307442763321</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7177,67 +7170,67 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3631177297534214</v>
+        <v>0.02974898395429348</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2847274682973682</v>
+        <v>-0.07343164326969065</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.135724924640571</v>
+        <v>-0.09590060655538424</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.05344164070720719</v>
+        <v>0.03998514041278377</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1224407453411339</v>
+        <v>0.1445422694995231</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9025341130604289</v>
+        <v>0.4365079365079365</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.06369478257858208</v>
+        <v>0.0007182735616988456</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3566324332753803</v>
+        <v>0.4098984628208118</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2055789028577925</v>
+        <v>-0.002474931135736743</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.135724924640571</v>
+        <v>0</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.4558476278786998</v>
+        <v>0.02900987336752658</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.05300254012386296</v>
+        <v>-0.3428119959245109</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.8483568893889354</v>
+        <v>0.05127439333567933</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.09816470117601539</v>
+        <v>-0.09590060655538446</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1972553972735562</v>
+        <v>0.07263630864195636</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4126586472383946</v>
+        <v>0.5190593084486794</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1524807499574862</v>
+        <v>-0.2938812180168442</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
       <c r="AE7" s="2" t="n">
-        <v>0.05993249576779425</v>
+        <v>0.03001018564506341</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.05743937134481081</v>
+        <v>-0.02853447743218596</v>
       </c>
     </row>
     <row r="8">
@@ -7287,73 +7280,73 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2023652129700342</v>
+        <v>-0.002541992331591914</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1332195175153694</v>
+        <v>-0.1024870706608754</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2613688299955147</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1308166044139103</v>
+        <v>0.1179700717241259</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1972259436194332</v>
+        <v>0.4311560897996646</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9317738791423001</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2613688299955145</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.07021832497726765</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8435842801631693</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2613688299955147</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.6278289649795483</v>
+        <v>0.4167443888284665</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.05886760772802146</v>
+        <v>-0.09518125989177606</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.168423383657608</v>
+        <v>0.7365876935246328</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.09816470117601528</v>
+        <v>-0.09590060655538435</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.05606303058118445</v>
+        <v>0.03900046714519556</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1144162074630566</v>
+        <v>0.06872512632346761</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.05236210357592652</v>
+        <v>-0.02781319391313286</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.1391324282831703</v>
+        <v>-0.003939165699813896</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.03097311804026792</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1755426495283825</v>
+        <v>-0.003939165699814007</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>0.05993249576779425</v>
+        <v>0.03001018564506341</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.002825702403289609</v>
+        <v>-0.009449106185097977</v>
       </c>
     </row>
     <row r="9">
@@ -7399,68 +7392,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3756062009719965</v>
+        <v>-0.06196743426201246</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2964977517155487</v>
+        <v>-0.1559580960616502</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1076918456382937</v>
+        <v>-0.1393867712832274</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.05135958986359192</v>
+        <v>0.09484283728054151</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1195503111112306</v>
+        <v>0.1265447516484733</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.6296296296296297</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.04156577035731202</v>
+        <v>-0.09810363394876553</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.3886956271326141</v>
+        <v>0.2706696117315508</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1341561289726186</v>
+        <v>0.3380324031619028</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.103046256281679</v>
+        <v>-0.1393867712832274</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4352640571746209</v>
+        <v>0.04006690906735533</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.06639170860459609</v>
+        <v>-0.3357503035048052</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.8100497601047697</v>
+        <v>0.07081749131535883</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.09816470117601539</v>
+        <v>-0.009046334590949612</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.2082242881065139</v>
+        <v>-0.02289994515420846</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.4460459870583235</v>
+        <v>0.3690507171713961</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1644634410525267</v>
+        <v>-0.286293748952863</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.05993249576779425</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.05649586949159147</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7509,74 +7498,70 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.2446774943609615</v>
+        <v>-0.02635171287505278</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.1730985015258593</v>
+        <v>-0.12391106231508</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.2481399708595511</v>
+        <v>-0.3140368405715118</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1149711421445071</v>
+        <v>0.1374734804365035</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1947762400381282</v>
+        <v>0.4239070163848245</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9278752436647173</v>
+        <v>1</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.2481399708595511</v>
+        <v>-0.3140368405715118</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.08938589878242542</v>
+        <v>-0.03355576731126375</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.8008873081800023</v>
+        <v>1.082066215357512</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.2481399708595511</v>
+        <v>-0.3140368405715118</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.6554643765062464</v>
+        <v>0.4193885979768135</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.07684384646156794</v>
+        <v>-0.09349250784231966</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.21985436700806</v>
+        <v>0.7412612823478749</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.09816470117601539</v>
+        <v>-0.07538615706116925</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.09322681046643999</v>
+        <v>0.01419911152213627</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1343753638404863</v>
+        <v>0.04127080529269977</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03627419519649622</v>
+        <v>-0.02599870622796696</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.1792194927849684</v>
+        <v>-0.0277155351576226</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.01361787953831128</v>
+        <v>-0.02568885146849087</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.1954996631863315</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.05993249576779425</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.003234618606485551</v>
-      </c>
+        <v>-0.002080119571849726</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7819,28 +7804,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003975565</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252798</v>
+        <v>0.1799741913752891</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213004998</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450097</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7849,10 +7834,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922789</v>
+        <v>0.5373300241682992</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7861,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7907,49 +7892,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.009474010358029972</v>
+        <v>0.1385354644109973</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.01189854660096956</v>
+        <v>0.07306049421285321</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.09228683758884382</v>
+        <v>0.1790388907472599</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3142199894496041</v>
+        <v>0.2472263231475021</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.9512670565302144</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.3372034926825385</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.03561910265103974</v>
+        <v>-0.03966012176582068</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8767479710097934</v>
+        <v>1.088345406940788</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.3372034926825385</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2564522869054031</v>
+        <v>0.7177752927802767</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.02290471080472434</v>
+        <v>0.1173757526199353</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8969824400054414</v>
+        <v>1.335818324857759</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.08406739461942148</v>
+        <v>-0.1166039321461161</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -8001,58 +7986,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>0.05550959933794908</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.005190714109256422</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.1161134555088488</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.1734081721485486</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9727095516569201</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809244</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.09388774724005255</v>
+        <v>0.1044258367867865</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6751222101795875</v>
+        <v>0.7673849036436503</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.3847468363930642</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.09925207039248651</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.7160345022383415</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.07769789874505417</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.05833257592660801</v>
+        <v>-0.07292338944926957</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.05626455174480016</v>
+        <v>0.150036421290288</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1084928273718074</v>
+        <v>-0.1938719562371833</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -8103,67 +8088,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.002069232786839126</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252243</v>
+        <v>-0.05945829907902977</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2944964900151588</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.1756474029500087</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2081723177968694</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>0.9590643274853801</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2852743938399765</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2963414873615395</v>
+        <v>0.03558104789742011</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884719</v>
+        <v>0.9207409857579846</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2935130093570599</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.3962431996451086</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452529</v>
+        <v>-0.09177393422698499</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010954</v>
+        <v>0.7374298509718111</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.09816470117601528</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.005371760459397468</v>
+        <v>-0.1234961067028122</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2517550941683937</v>
+        <v>0.07834847991691252</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1968303023944805</v>
+        <v>-0.1871793676894478</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1958359094029314</v>
+        <v>0.7987676932469374</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1468927565683013</v>
+        <v>-0.4433148926414667</v>
       </c>
     </row>
     <row r="6">
@@ -8213,73 +8198,73 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>0.04258757152117965</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.01736962112509388</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3176543999139079</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.1782173967914346</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.2265591129258874</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9844054580896686</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3167032016699218</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.09388774724005255</v>
+        <v>-0.009956816516820788</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6751222101795875</v>
+        <v>1.022179432837026</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3167032016699219</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.5258194887919554</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.007487354826476555</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.9785782761829468</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.0981647011760155</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.05833257592660801</v>
+        <v>-0.08427308229652264</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.05626455174480016</v>
+        <v>0.03092999251849937</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1084928273718074</v>
+        <v>-0.1117467487133514</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0</v>
+        <v>-0.01224245409504054</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1035675275728717</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>0.1018761326556643</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.1958359094029314</v>
+        <v>0.7987676932469374</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.06234305370981008</v>
+        <v>-0.07008181681004189</v>
       </c>
     </row>
     <row r="7">
@@ -8325,64 +8310,68 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.07578698723968413</v>
+        <v>0.3631177297534214</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.07837079277948233</v>
+        <v>0.2847274682973682</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.05508953650041504</v>
+        <v>-0.135724924640571</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03866152495059907</v>
+        <v>0.05344164070720719</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1334505542485514</v>
+        <v>0.1224407453411339</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.8522727272727273</v>
+        <v>0.9025341130604289</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.04935572881567429</v>
+        <v>-0.06369478257858208</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2253748063110765</v>
+        <v>0.3566324332753803</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2201403153455292</v>
+        <v>0.2055789028577925</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.05508953650041504</v>
+        <v>-0.135724924640571</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1316398992227177</v>
+        <v>0.4558476278786998</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1199665708601776</v>
+        <v>-0.05300254012386296</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.4604313708086334</v>
+        <v>0.8483568893889354</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02626816353601968</v>
+        <v>-0.09816470117601539</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.06569062323668429</v>
+        <v>0.1972553972735562</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.183229242464038</v>
+        <v>0.4126586472383946</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.09933714871902843</v>
+        <v>-0.1524807499574862</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.05993249576779425</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.05743937134481081</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8431,70 +8420,74 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.01542806786165696</v>
+        <v>0.2023652129700342</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.017866904451175</v>
+        <v>0.1332195175153694</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1717607303038212</v>
+        <v>-0.2613688299955147</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.08173471827038334</v>
+        <v>0.1308166044139103</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.24966224659012</v>
+        <v>0.1972259436194332</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.9317738791423001</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1717607303038212</v>
+        <v>-0.2613688299955145</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.06759548807757687</v>
+        <v>0.07021832497726765</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7661007595343929</v>
+        <v>0.8435842801631693</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1717607303038212</v>
+        <v>-0.2613688299955147</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2260081174781101</v>
+        <v>0.6278289649795483</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.04657998669135299</v>
+        <v>0.05886760772802146</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7904991416642364</v>
+        <v>1.168423383657608</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.09816470117601528</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.005898178103183938</v>
+        <v>0.05606303058118445</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03087658903228241</v>
+        <v>0.1144162074630566</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02423026305461695</v>
+        <v>-0.05236210357592652</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.06820959543439176</v>
+        <v>0.1391324282831703</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.02403560989581677</v>
+        <v>-0.03097311804026792</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.09451697855529484</v>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+        <v>0.1755426495283825</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.05993249576779425</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.002825702403289609</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8539,64 +8532,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.06770351030249933</v>
+        <v>0.3756062009719965</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.06546433761925685</v>
+        <v>0.2964977517155487</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1256532754890514</v>
+        <v>-0.1076918456382937</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.09908234898376832</v>
+        <v>0.05135958986359192</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1594905466415855</v>
+        <v>0.1195503111112306</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1109926240399126</v>
+        <v>-0.04156577035731202</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1459252152953721</v>
+        <v>0.3886956271326141</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.495058057969847</v>
+        <v>0.1341561289726186</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1256532754890514</v>
+        <v>-0.103046256281679</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.04869376217566601</v>
+        <v>0.4352640571746209</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1844706356864146</v>
+        <v>-0.06639170860459609</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.1703141357654758</v>
+        <v>0.8100497601047697</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.01948719111785824</v>
+        <v>-0.09816470117601539</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.07645320223069119</v>
+        <v>0.2082242881065139</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1065122421573377</v>
+        <v>0.4460459870583235</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1653532942674958</v>
+        <v>-0.1644634410525267</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.05993249576779425</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.05649586949159147</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8645,70 +8642,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.0576177176261522</v>
+        <v>0.2446774943609615</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.05535432107024763</v>
+        <v>0.1730985015258593</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.189144434109547</v>
+        <v>-0.2481399708595511</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1063217557490388</v>
+        <v>0.1149711421445071</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2575434518891145</v>
+        <v>0.1947762400381282</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9278752436647173</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.189144434109547</v>
+        <v>-0.2481399708595511</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.04518799735828538</v>
+        <v>0.08938589878242542</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.843636926652047</v>
+        <v>0.8008873081800023</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.189144434109547</v>
+        <v>-0.2481399708595511</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.1622073301537454</v>
+        <v>0.6554643765062464</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.09619543917711837</v>
+        <v>0.07684384646156794</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.567345795757103</v>
+        <v>1.21985436700806</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.09816470117601539</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.06646206568546198</v>
+        <v>0.09322681046643999</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.009239781964962557</v>
+        <v>0.1343753638404863</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.07500878285142021</v>
+        <v>-0.03627419519649622</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.008633079525771525</v>
+        <v>0.1792194927849684</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.04451987875779728</v>
+        <v>-0.01361787953831128</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.03755891769403852</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0.1954996631863315</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.05993249576779425</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0.003234618606485551</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8721,7 +8722,1139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651871976</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645823</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947869</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>0.01313097569578958</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.008165739615837442</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.09177270078849505</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.3124853358722013</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.9662921348314607</v>
+      </c>
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.03561910265103974</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.8767479710097934</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.2610039667055915</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.02650913155708057</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.8837335750983453</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.08406739461942148</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>-0.04521242326464603</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.04989172518949392</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.07269182521527755</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.2314419517208828</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.09388774724005255</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.6751222101795875</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.1250839088436306</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.1314389641828525</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.4235217239987224</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>-0.05758722254086346</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.05626455174480016</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.1077871770832377</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.0100920662696089</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.2963414873615395</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.02542419299884719</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0.001910724177658807</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.2517550941683937</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1995952492262231</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1958359094029314</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.1468927565683013</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.04521242326464603</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.04989172518949392</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.07269182521527755</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.2314419517208828</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.09388774724005255</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.6751222101795875</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.1250839088436306</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1314389641828525</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.4235217239987224</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>-0.05758722254086346</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.05626455174480016</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.1077871770832377</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1958359094029314</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.06234305370981008</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.07968418090963625</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.07439277537707478</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.05508953650041504</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.03844613873460084</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.1327729316998424</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.8426966292134831</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-0.04935572881567429</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.2253748063110765</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.2201403153455292</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.05508953650041504</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.1357394281296733</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.1232129387322111</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.4596002567200496</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.02626816353601968</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0.06569062323668451</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.183229242464038</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.09933714871902843</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.01910660263229569</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.01411208070561965</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1717607303038212</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.08127936810749053</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.2483072200002718</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.9438202247191011</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1717607303038212</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.06759548807757687</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.7661007595343929</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1717607303038212</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.2304495088793996</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.05009707138071995</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.7802792077538445</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0.005898178103183715</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.03087658903228241</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.02423026305461684</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0.06736474946276938</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>-0.02403560989581677</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0.09365132609892579</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.06432613167525802</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.06891175955706641</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-0.1256532754890514</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.09876338775909906</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.1587555036683463</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-0.1109926240399126</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.1459252152953721</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.495058057969847</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>-0.1256532754890514</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.0524928067264423</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.1874790535934427</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.177735443414284</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.01948719111785824</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>-0.07645320223069108</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.1065122421573377</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1653532942674958</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.05420380175888029</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.05883903799234269</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.189144434109547</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.1058836968606909</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.2561777058367906</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-0.189144434109547</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.04518799735828538</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.843636926652047</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.189144434109547</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.1664175939921924</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.0995294967159559</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.5634734872205083</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>-0.06646206568546209</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.009239781964962557</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>-0.0750087828514201</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>-0.009417150697517362</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>-0.04451987875779728</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0.0367383133148218</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8827,24 +9960,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.496398891966759</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -8875,20 +10006,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>155</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -8921,20 +10052,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>-131</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>523</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8970,16 +10105,14 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -9009,24 +10142,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-174</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9057,21 +10188,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-114</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-174</v>
+      </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9088,37 +10221,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.08476454293628809</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9145,27 +10276,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>81</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9192,14 +10321,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -9209,10 +10338,10 @@
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9239,27 +10368,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-10</v>
+        <v>39</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9286,27 +10415,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9333,27 +10462,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9370,37 +10499,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-35</v>
+        <v>-21</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9417,24 +10546,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -9444,10 +10573,10 @@
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9474,27 +10603,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -9521,27 +10650,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -9568,27 +10697,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-21</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.52046783625731</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -9615,14 +10744,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -9632,7 +10761,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -9641,6 +10770,147 @@
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
